--- a/branches/release-candidate/StructureDefinition-be-medicationline.xlsx
+++ b/branches/release-candidate/StructureDefinition-be-medicationline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T08:07:39+00:00</t>
+    <t>2026-03-27T06:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -377,7 +377,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -724,7 +724,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -824,7 +824,7 @@
     <t>MedicationStatement.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -849,7 +849,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1|CarePlan|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -871,7 +871,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -937,7 +937,7 @@
     <t>A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -958,7 +958,7 @@
     <t>A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -971,7 +971,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>What medication was taken</t>
@@ -986,7 +986,7 @@
     <t>A coded concept identifying the substance or product being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1119,7 +1119,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1201,7 +1201,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
     <t>A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1247,7 +1247,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1417,7 +1417,7 @@
     <t>A coded concept identifying additional instructions such as "take with water" or "avoid operating heavy machinery".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.additionalInstruction</t>
@@ -1479,7 +1479,7 @@
     <t>A coded concept identifying the precondition that should be met or evaluated prior to consuming or administering a medication dose.  For example "pain", "30 minutes prior to sexual intercourse", "on flare-up" etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>Dosage.asNeeded[x]</t>
@@ -1509,7 +1509,7 @@
     <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -1536,7 +1536,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.route</t>
@@ -1566,7 +1566,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1618,7 +1618,7 @@
     <t>The kind of dose or rate specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/dose-rate-type</t>
+    <t>http://hl7.org/fhir/ValueSet/dose-rate-type|4.0.1</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.type</t>
@@ -1631,7 +1631,7 @@
   </si>
   <si>
     <t>Range
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>Amount of medication per dose</t>
@@ -1656,7 +1656,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>Amount of medication per unit of time</t>
@@ -1713,7 +1713,7 @@
     <t>MedicationStatement.dosage.maxDosePerAdministration</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -2073,15 +2073,15 @@
   <dimension ref="A1:AN70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="86.25" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.5859375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.47265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="73.9453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.9375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2092,26 +2092,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="198.02734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.25" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="140.73046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="120.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3142,7 +3142,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>163</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>186</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>237</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>277</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>286</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>295</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>319</v>
       </c>
@@ -6342,7 +6342,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>342</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>356</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>364</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>370</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>382</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>391</v>
       </c>
@@ -7246,7 +7246,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>398</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>404</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>412</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>417</v>
       </c>
@@ -10106,12 +10106,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN70">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
